--- a/energy/ZnPc2_0_scan.xlsx
+++ b/energy/ZnPc2_0_scan.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ZnPc2_0_scan" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="energies_scan" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,23 +20,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">scan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncorrected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total+CP-gCP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -52,6 +73,17 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -96,8 +128,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -120,7 +160,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF7E0021"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -148,7 +188,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FF83CAFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
@@ -161,7 +201,7 @@
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF004586"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF579D1C"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -208,32 +248,32 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="0"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>ZnPc2_0_scan!$F$2:$F$16</c:f>
+              <c:f>energies_scan!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -244,94 +284,97 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ZnPc2_0_scan!$G$2:$G$16</c:f>
+              <c:f>energies_scan!$H$2:$H$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>-0.00683929279784934</c:v>
+                  <c:v>-19.4232591275</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.0213413689843947</c:v>
+                  <c:v>-19.00813462</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.0257056663995172</c:v>
+                  <c:v>-18.50958336</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.0242893232816641</c:v>
+                  <c:v>-17.84830378</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.0247670786584422</c:v>
+                  <c:v>-17.059713235</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.0255969706358883</c:v>
+                  <c:v>-16.18587054</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.0214404070611636</c:v>
+                  <c:v>-14.3347122825</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.0180915875826031</c:v>
+                  <c:v>-12.5123456075</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.0169176021590829</c:v>
+                  <c:v>-10.833738555</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.0111609028663224</c:v>
+                  <c:v>-9.319229655</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.00594941610506794</c:v>
+                  <c:v>-7.94597916250001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.00309115044910868</c:v>
+                  <c:v>-5.49502252000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.00202748584069923</c:v>
+                  <c:v>-3.41658941</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.000993152209957771</c:v>
+                  <c:v>-1.8004411975</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.000125418529933086</c:v>
+                  <c:v>-0.750644992500007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -363,32 +406,32 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="0"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>ZnPc2_0_scan!$F$2:$F$16</c:f>
+              <c:f>energies_scan!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -399,94 +442,97 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ZnPc2_0_scan!$H$2:$H$16</c:f>
+              <c:f>energies_scan!$I$2:$I$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.000214790999999992</c:v>
+                  <c:v>0.134781352499995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.000172941999999995</c:v>
+                  <c:v>0.108521104999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.000160441999999997</c:v>
+                  <c:v>0.0997354774999974</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.000159914999999997</c:v>
+                  <c:v>0.100677354999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.000147622</c:v>
+                  <c:v>0.100346662499998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.000122821999999995</c:v>
+                  <c:v>0.092632805</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.000110085999999995</c:v>
+                  <c:v>0.0770708049999967</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.17579999999912E-005</c:v>
+                  <c:v>0.0690789649999971</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.22290000000009E-005</c:v>
+                  <c:v>0.0450281449999945</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.49839999999979E-005</c:v>
+                  <c:v>0.0327736975000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.78259999999986E-005</c:v>
+                  <c:v>0.0282274599999987</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.31599999999133E-006</c:v>
+                  <c:v>0.0111858149999991</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.97400000000281E-006</c:v>
+                  <c:v>0.00333578999999456</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.70999999990884E-007</c:v>
+                  <c:v>0.00186618500000176</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.99999999894729E-009</c:v>
+                  <c:v>0.00035830249999428</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -518,7 +564,467 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>energies_scan!$G$2:$G$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>energies_scan!$J$2:$J$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>-23.5801340069793</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-32.2913225561933</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-34.9449333543225</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-33.87793209743</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-32.2009169368835</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-31.6345796006772</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-30.3197405542801</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-25.8971220789635</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-22.1411816225009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-19.9022513194564</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-14.9212182534143</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-9.21709531421129</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.35295053384516</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-3.07082238343355</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1.37348970799621</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="579d1c"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="579d1c"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="579d1c"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>energies_scan!$G$2:$G$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>energies_scan!$K$2:$K$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>-4.29165623179188</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-13.3917090411319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-16.5350854717531</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-16.1303056725455</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-15.2415503643806</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-15.5413418655917</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-16.0620990763027</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-13.4538554360165</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-11.3524712126491</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-10.615795361673</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-7.00346655090016</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-3.73325860878367</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.93969691366419</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1.27224737074584</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.62320301745558</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="55984916"/>
+        <c:axId val="46823870"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="55984916"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="46823870"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="46823870"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="55984916"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="span"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -534,19 +1040,14 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="0"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>ZnPc2_0_scan!$F$2:$F$16</c:f>
+              <c:f>energies_scan!$G$2:$G$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -554,39 +1055,45 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
@@ -594,65 +1101,845 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ZnPc2_0_scan!$I$2:$I$16</c:f>
+              <c:f>energies_scan!$H$2:$H$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>-0.030953401</c:v>
+                  <c:v>-19.4232591275</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.030291848</c:v>
+                  <c:v>-19.00813462</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.028443512</c:v>
+                  <c:v>-18.50958336</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.027186794</c:v>
+                  <c:v>-17.84830378</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.025794216</c:v>
+                  <c:v>-17.059713235</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.022844163</c:v>
+                  <c:v>-16.18587054</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.019939993</c:v>
+                  <c:v>-14.3347122825</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.017264922</c:v>
+                  <c:v>-12.5123456075</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.014851362</c:v>
+                  <c:v>-10.833738555</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.012662915</c:v>
+                  <c:v>-9.319229655</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.00875700800000001</c:v>
+                  <c:v>-7.94597916250001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.00544476400000001</c:v>
+                  <c:v>-5.49502252000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.002869229</c:v>
+                  <c:v>-3.41658941</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.00119624700000001</c:v>
+                  <c:v>-1.8004411975</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.000419263000000003</c:v>
+                  <c:v>-0.750644992500007</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.263087532500002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="38140823"/>
-        <c:axId val="67058319"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>energies_scan!$G$2:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>energies_scan!$I$2:$I$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0.134781352499995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.108521104999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0997354774999974</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.100677354999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.100346662499998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.092632805</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.0770708049999967</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.0690789649999971</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.0450281449999945</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0327736975000005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.0282274599999987</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.0111858149999991</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.00333578999999456</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.00186618500000176</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.00035830249999428</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.25499999933942E-006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>energies_scan!$G$2:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>energies_scan!$J$2:$J$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>-23.5801340069793</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-32.2913225561933</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-34.9449333543225</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-33.87793209743</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-32.2009169368835</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-31.6345796006772</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-30.3197405542801</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-25.8971220789635</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-22.1411816225009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-19.9022513194564</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-14.9212182534143</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-9.21709531421129</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.35295053384516</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-3.07082238343355</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1.37348970799621</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.341786411554494</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="579d1c"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="579d1c"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="579d1c"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>energies_scan!$G$2:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>energies_scan!$K$2:$K$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>-4.29165623179188</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-13.3917090411319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-16.5350854717531</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-16.1303056725455</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-15.2415503643806</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-15.5413418655917</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-16.0620990763027</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-13.4538554360165</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-11.3524712126491</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-10.615795361673</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-7.00346655090016</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-3.73325860878367</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.93969691366419</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1.27224737074584</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.62320301745558</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.0787001338107984</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7e0021"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="7e0021"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7e0021"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>energies_scan!$G$2:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>energies_scan!$L$2:$L$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>3.992</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.854</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.756</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.594</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.176</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.786</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.38</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.986</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.862</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.456</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.758</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.344</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="83caff"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="83caff"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="83caff"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>energies_scan!$G$2:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>energies_scan!$M$2:$M$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>-19.7229153594793</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-28.5458436611933</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-31.2886688318225</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-30.38460945243</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-28.9212635993835</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-28.5512124056772</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-27.6108113592801</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-23.5862010439635</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-20.2002097675009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-18.0730250169564</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-13.4934457134143</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-8.47028112921129</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.01228632384515</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="9357490"/>
+        <c:axId val="32276884"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="38140823"/>
+        <c:axId val="9357490"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -663,7 +1950,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
@@ -680,12 +1967,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67058319"/>
+        <c:crossAx val="32276884"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="67058319"/>
+        <c:axId val="32276884"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -693,19 +1980,19 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="b3b3b3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:ln>
             <a:solidFill>
               <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
@@ -722,13 +2009,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38140823"/>
+        <c:crossAx val="9357490"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:solidFill>
             <a:srgbClr val="b3b3b3"/>
           </a:solidFill>
@@ -740,7 +2027,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -763,7 +2050,7 @@
     <a:solidFill>
       <a:srgbClr val="ffffff"/>
     </a:solidFill>
-    <a:ln w="0">
+    <a:ln>
       <a:noFill/>
     </a:ln>
   </c:spPr>
@@ -774,16 +2061,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>491400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>102960</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>273600</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>561240</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>343440</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>33840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -791,8 +2078,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9496800" y="1078200"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="10916640" y="2158920"/>
+        <a:ext cx="5768280" cy="3239280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -802,127 +2089,52 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>641520</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>35640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>705240</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>24120</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4774680" y="3124080"/>
+        <a:ext cx="5759640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.29"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="8" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -938,6 +2150,28 @@
       <c r="D1" s="0" t="n">
         <v>-3446.28179291571</v>
       </c>
+      <c r="E1" s="0" t="n">
+        <f aca="false">D1-C1-B1</f>
+        <v>-3446.27646200871</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
@@ -952,21 +2186,36 @@
       <c r="D2" s="0" t="n">
         <v>-6892.60116373422</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="E2" s="0" t="n">
+        <f aca="false">D2-C2-B2</f>
+        <v>-6892.55976331022</v>
+      </c>
+      <c r="G2" s="0" t="n">
         <f aca="false">A2/10</f>
         <v>0</v>
       </c>
-      <c r="G2" s="0" t="n">
-        <f aca="false">D2-C2-B2-2*(D$1-C$1-B$1)</f>
-        <v>-0.00683929279784934</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <f aca="false">C2-2*C$1</f>
-        <v>0.000214790999999992</v>
-      </c>
-      <c r="I2" s="0" t="n">
-        <f aca="false">B2-2*B$1</f>
-        <v>-0.030953401</v>
+      <c r="H2" s="1" t="n">
+        <f aca="false">627.5*(B2-2*B$1)</f>
+        <v>-19.4232591275</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <f aca="false">627.5*(C2-2*C$1)</f>
+        <v>0.134781352499995</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <f aca="false">627.5*(D2-2*D$1)</f>
+        <v>-23.5801340069793</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <f aca="false">627.5*(E2-2*E$1)</f>
+        <v>-4.29165623179188</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <f aca="false">J2-I2+L2</f>
+        <v>-19.7229153594793</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -982,413 +2231,651 @@
       <c r="D3" s="0" t="n">
         <v>-6892.61504610641</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="E3" s="0" t="n">
+        <f aca="false">D3-C3-B3</f>
+        <v>-6892.57426538641</v>
+      </c>
+      <c r="G3" s="0" t="n">
         <f aca="false">A3/10</f>
         <v>1</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <f aca="false">D3-C3-B3-2*(D$1-C$1-B$1)</f>
-        <v>-0.0213413689843947</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <f aca="false">C3-2*C$1</f>
-        <v>0.000172941999999995</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <f aca="false">B3-2*B$1</f>
-        <v>-0.030291848</v>
+      <c r="H3" s="1" t="n">
+        <f aca="false">627.5*(B3-2*B$1)</f>
+        <v>-19.00813462</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <f aca="false">627.5*(C3-2*C$1)</f>
+        <v>0.108521104999997</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <f aca="false">627.5*(D3-2*D$1)</f>
+        <v>-32.2913225561933</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <f aca="false">627.5*(E3-2*E$1)</f>
+        <v>-13.3917090411319</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <f aca="false">J3-I3+L3</f>
+        <v>-28.5458436611933</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>-0.102223254</v>
+        <v>-0.103277086</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.06327837</v>
+        <v>0.063276869</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>-6892.61757456783</v>
-      </c>
-      <c r="F4" s="0" t="n">
+        <v>-6892.61927496824</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <f aca="false">D4-C4-B4</f>
+        <v>-6892.57927475124</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <f aca="false">A4/10</f>
-        <v>2</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <f aca="false">D4-C4-B4-2*(D$1-C$1-B$1)</f>
-        <v>-0.0257056663995172</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <f aca="false">C4-2*C$1</f>
-        <v>0.000160441999999997</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <f aca="false">B4-2*B$1</f>
-        <v>-0.028443512</v>
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <f aca="false">627.5*(B4-2*B$1)</f>
+        <v>-18.50958336</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <f aca="false">627.5*(C4-2*C$1)</f>
+        <v>0.0997354774999974</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <f aca="false">627.5*(D4-2*D$1)</f>
+        <v>-34.9449333543225</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <f aca="false">627.5*(E4-2*E$1)</f>
+        <v>-16.5350854717531</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>3.756</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <f aca="false">J4-I4+L4</f>
+        <v>-31.2886688318225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>-0.100966536</v>
+        <v>-0.102223254</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.063277843</v>
+        <v>0.06327837</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>-6892.61490203371</v>
+        <v>-6892.61757456783</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false">D5-C5-B5</f>
+        <v>-6892.57862968383</v>
       </c>
       <c r="G5" s="0" t="n">
-        <f aca="false">D5-C5-B5-2*(D$1-C$1-B$1)</f>
-        <v>-0.0242893232816641</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <f aca="false">C5-2*C$1</f>
-        <v>0.000159914999999997</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <f aca="false">B5-2*B$1</f>
-        <v>-0.027186794</v>
+        <f aca="false">A5/10</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <f aca="false">627.5*(B5-2*B$1)</f>
+        <v>-17.84830378</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <f aca="false">627.5*(C5-2*C$1)</f>
+        <v>0.100677354999998</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <f aca="false">627.5*(D5-2*D$1)</f>
+        <v>-33.87793209743</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <f aca="false">627.5*(E5-2*E$1)</f>
+        <v>-16.1303056725455</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>3.594</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <f aca="false">J5-I5+L5</f>
+        <v>-30.38460945243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>-0.099573958</v>
+        <v>-0.100966536</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.06326555</v>
+        <v>0.063277843</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>-6892.61399950409</v>
-      </c>
-      <c r="F6" s="0" t="n">
+        <v>-6892.61490203371</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <f aca="false">D6-C6-B6</f>
+        <v>-6892.57721334071</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <f aca="false">A6/10</f>
-        <v>3</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <f aca="false">D6-C6-B6-2*(D$1-C$1-B$1)</f>
-        <v>-0.0247670786584422</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <f aca="false">C6-2*C$1</f>
-        <v>0.000147622</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <f aca="false">B6-2*B$1</f>
-        <v>-0.025794216</v>
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <f aca="false">627.5*(B6-2*B$1)</f>
+        <v>-17.059713235</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <f aca="false">627.5*(C6-2*C$1)</f>
+        <v>0.100346662499998</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <f aca="false">627.5*(D6-2*D$1)</f>
+        <v>-32.2009169368835</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <f aca="false">627.5*(E6-2*E$1)</f>
+        <v>-15.2415503643806</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <f aca="false">J6-I6+L6</f>
+        <v>-28.9212635993835</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>-0.096623905</v>
+        <v>-0.099573958</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.06324075</v>
+        <v>0.06326555</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>-6892.61190414306</v>
-      </c>
-      <c r="F7" s="0" t="n">
+        <v>-6892.61399950409</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <f aca="false">D7-C7-B7</f>
+        <v>-6892.57769109609</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <f aca="false">A7/10</f>
-        <v>4</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <f aca="false">D7-C7-B7-2*(D$1-C$1-B$1)</f>
-        <v>-0.0255969706358883</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <f aca="false">C7-2*C$1</f>
-        <v>0.000122821999999995</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <f aca="false">B7-2*B$1</f>
-        <v>-0.022844163</v>
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <f aca="false">627.5*(B7-2*B$1)</f>
+        <v>-16.18587054</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <f aca="false">627.5*(C7-2*C$1)</f>
+        <v>0.092632805</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <f aca="false">627.5*(D7-2*D$1)</f>
+        <v>-31.6345796006772</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <f aca="false">627.5*(E7-2*E$1)</f>
+        <v>-15.5413418655917</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>3.176</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <f aca="false">J7-I7+L7</f>
+        <v>-28.5512124056772</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>-0.093719735</v>
+        <v>-0.096623905</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.063228014</v>
+        <v>0.06324075</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>-6892.60485614549</v>
-      </c>
-      <c r="F8" s="0" t="n">
+        <v>-6892.61190414306</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <f aca="false">D8-C8-B8</f>
+        <v>-6892.57852098806</v>
+      </c>
+      <c r="G8" s="0" t="n">
         <f aca="false">A8/10</f>
-        <v>5</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <f aca="false">D8-C8-B8-2*(D$1-C$1-B$1)</f>
-        <v>-0.0214404070611636</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <f aca="false">C8-2*C$1</f>
-        <v>0.000110085999999995</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <f aca="false">B8-2*B$1</f>
-        <v>-0.019939993</v>
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <f aca="false">627.5*(B8-2*B$1)</f>
+        <v>-14.3347122825</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <f aca="false">627.5*(C8-2*C$1)</f>
+        <v>0.0770708049999967</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <f aca="false">627.5*(D8-2*D$1)</f>
+        <v>-30.3197405542801</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <f aca="false">627.5*(E8-2*E$1)</f>
+        <v>-16.0620990763027</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>2.786</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <f aca="false">J8-I8+L8</f>
+        <v>-27.6108113592801</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>-0.091044664</v>
+        <v>-0.093719735</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.063189686</v>
+        <v>0.063228014</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>-6892.59887058301</v>
-      </c>
-      <c r="F9" s="0" t="n">
+        <v>-6892.60485614549</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <f aca="false">D9-C9-B9</f>
+        <v>-6892.57436442449</v>
+      </c>
+      <c r="G9" s="0" t="n">
         <f aca="false">A9/10</f>
-        <v>6</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <f aca="false">D9-C9-B9-2*(D$1-C$1-B$1)</f>
-        <v>-0.0180915875826031</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <f aca="false">C9-2*C$1</f>
-        <v>7.17579999999912E-005</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <f aca="false">B9-2*B$1</f>
-        <v>-0.017264922</v>
+        <v>5</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <f aca="false">627.5*(B9-2*B$1)</f>
+        <v>-12.5123456075</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <f aca="false">627.5*(C9-2*C$1)</f>
+        <v>0.0690789649999971</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <f aca="false">627.5*(D9-2*D$1)</f>
+        <v>-25.8971220789635</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <f aca="false">627.5*(E9-2*E$1)</f>
+        <v>-13.4538554360165</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <f aca="false">J9-I9+L9</f>
+        <v>-23.5862010439635</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>-0.088631104</v>
+        <v>-0.091044664</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.063170157</v>
+        <v>0.063189686</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>-6892.59530256659</v>
-      </c>
-      <c r="F10" s="0" t="n">
+        <v>-6892.59887058301</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <f aca="false">D10-C10-B10</f>
+        <v>-6892.57101560501</v>
+      </c>
+      <c r="G10" s="0" t="n">
         <f aca="false">A10/10</f>
-        <v>7</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <f aca="false">D10-C10-B10-2*(D$1-C$1-B$1)</f>
-        <v>-0.0169176021590829</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <f aca="false">C10-2*C$1</f>
-        <v>5.22290000000009E-005</v>
-      </c>
-      <c r="I10" s="0" t="n">
-        <f aca="false">B10-2*B$1</f>
-        <v>-0.014851362</v>
+        <v>6</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <f aca="false">627.5*(B10-2*B$1)</f>
+        <v>-10.833738555</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <f aca="false">627.5*(C10-2*C$1)</f>
+        <v>0.0450281449999945</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <f aca="false">627.5*(D10-2*D$1)</f>
+        <v>-22.1411816225009</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <f aca="false">627.5*(E10-2*E$1)</f>
+        <v>-11.3524712126491</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <f aca="false">J10-I10+L10</f>
+        <v>-20.2002097675009</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>-0.086442657</v>
+        <v>-0.088631104</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.063162912</v>
+        <v>0.063170157</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>-6892.58736466529</v>
-      </c>
-      <c r="F11" s="0" t="n">
+        <v>-6892.59530256659</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <f aca="false">D11-C11-B11</f>
+        <v>-6892.56984161959</v>
+      </c>
+      <c r="G11" s="0" t="n">
         <f aca="false">A11/10</f>
-        <v>8</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <f aca="false">D11-C11-B11-2*(D$1-C$1-B$1)</f>
-        <v>-0.0111609028663224</v>
-      </c>
-      <c r="H11" s="0" t="n">
-        <f aca="false">C11-2*C$1</f>
-        <v>4.49839999999979E-005</v>
-      </c>
-      <c r="I11" s="0" t="n">
-        <f aca="false">B11-2*B$1</f>
-        <v>-0.012662915</v>
+        <v>7</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <f aca="false">627.5*(B11-2*B$1)</f>
+        <v>-9.319229655</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <f aca="false">627.5*(C11-2*C$1)</f>
+        <v>0.0327736975000005</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <f aca="false">627.5*(D11-2*D$1)</f>
+        <v>-19.9022513194564</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <f aca="false">627.5*(E11-2*E$1)</f>
+        <v>-10.615795361673</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <f aca="false">J11-I11+L11</f>
+        <v>-18.0730250169564</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>-0.08253675</v>
+        <v>-0.086442657</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.063135754</v>
+        <v>0.063162912</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>-6892.57827442953</v>
-      </c>
-      <c r="F12" s="0" t="n">
+        <v>-6892.58736466529</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <f aca="false">D12-C12-B12</f>
+        <v>-6892.56408492029</v>
+      </c>
+      <c r="G12" s="0" t="n">
         <f aca="false">A12/10</f>
-        <v>10</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <f aca="false">D12-C12-B12-2*(D$1-C$1-B$1)</f>
-        <v>-0.00594941610506794</v>
-      </c>
-      <c r="H12" s="0" t="n">
-        <f aca="false">C12-2*C$1</f>
-        <v>1.78259999999986E-005</v>
-      </c>
-      <c r="I12" s="0" t="n">
-        <f aca="false">B12-2*B$1</f>
-        <v>-0.00875700800000001</v>
+        <v>8</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <f aca="false">627.5*(B12-2*B$1)</f>
+        <v>-7.94597916250001</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <f aca="false">627.5*(C12-2*C$1)</f>
+        <v>0.0282274599999987</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <f aca="false">627.5*(D12-2*D$1)</f>
+        <v>-14.9212182534143</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <f aca="false">627.5*(E12-2*E$1)</f>
+        <v>-7.00346655090016</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>1.456</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <f aca="false">J12-I12+L12</f>
+        <v>-13.4934457134143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>-0.079224506</v>
+        <v>-0.08253675</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.063123244</v>
+        <v>0.063135754</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>-6892.57211642988</v>
-      </c>
-      <c r="F13" s="0" t="n">
+        <v>-6892.57827442953</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <f aca="false">D13-C13-B13</f>
+        <v>-6892.55887343353</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <f aca="false">A13/10</f>
-        <v>12</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <f aca="false">D13-C13-B13-2*(D$1-C$1-B$1)</f>
-        <v>-0.00309115044910868</v>
-      </c>
-      <c r="H13" s="0" t="n">
-        <f aca="false">C13-2*C$1</f>
-        <v>5.31599999999133E-006</v>
-      </c>
-      <c r="I13" s="0" t="n">
-        <f aca="false">B13-2*B$1</f>
-        <v>-0.00544476400000001</v>
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <f aca="false">627.5*(B13-2*B$1)</f>
+        <v>-5.49502252000001</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <f aca="false">627.5*(C13-2*C$1)</f>
+        <v>0.0111858149999991</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <f aca="false">627.5*(D13-2*D$1)</f>
+        <v>-9.21709531421129</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <f aca="false">627.5*(E13-2*E$1)</f>
+        <v>-3.73325860878367</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <f aca="false">J13-I13+L13</f>
+        <v>-8.47028112921129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>-0.076648971</v>
+        <v>-0.079224506</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.063120902</v>
+        <v>0.063123244</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>-6892.56847957227</v>
-      </c>
-      <c r="F14" s="0" t="n">
+        <v>-6892.57211642988</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <f aca="false">D14-C14-B14</f>
+        <v>-6892.55601516788</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <f aca="false">A14/10</f>
-        <v>14</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <f aca="false">D14-C14-B14-2*(D$1-C$1-B$1)</f>
-        <v>-0.00202748584069923</v>
-      </c>
-      <c r="H14" s="0" t="n">
-        <f aca="false">C14-2*C$1</f>
-        <v>2.97400000000281E-006</v>
-      </c>
-      <c r="I14" s="0" t="n">
-        <f aca="false">B14-2*B$1</f>
-        <v>-0.002869229</v>
+        <v>12</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <f aca="false">627.5*(B14-2*B$1)</f>
+        <v>-3.41658941</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <f aca="false">627.5*(C14-2*C$1)</f>
+        <v>0.00333578999999456</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <f aca="false">627.5*(D14-2*D$1)</f>
+        <v>-5.35295053384516</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <f aca="false">627.5*(E14-2*E$1)</f>
+        <v>-1.93969691366419</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <f aca="false">J14-I14+L14</f>
+        <v>-5.01228632384515</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>-0.074975989</v>
+        <v>-0.076648971</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.063118499</v>
+        <v>0.063120902</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>-6892.56577465964</v>
-      </c>
-      <c r="F15" s="0" t="n">
+        <v>-6892.56847957227</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <f aca="false">D15-C15-B15</f>
+        <v>-6892.55495150327</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <f aca="false">A15/10</f>
-        <v>16</v>
-      </c>
-      <c r="G15" s="0" t="n">
-        <f aca="false">D15-C15-B15-2*(D$1-C$1-B$1)</f>
-        <v>-0.000993152209957771</v>
-      </c>
-      <c r="H15" s="0" t="n">
-        <f aca="false">C15-2*C$1</f>
-        <v>5.70999999990884E-007</v>
-      </c>
-      <c r="I15" s="0" t="n">
-        <f aca="false">B15-2*B$1</f>
-        <v>-0.00119624700000001</v>
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <f aca="false">627.5*(B15-2*B$1)</f>
+        <v>-1.8004411975</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <f aca="false">627.5*(C15-2*C$1)</f>
+        <v>0.00186618500000176</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <f aca="false">627.5*(D15-2*D$1)</f>
+        <v>-3.07082238343355</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <f aca="false">627.5*(E15-2*E$1)</f>
+        <v>-1.27224737074584</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>-0.074975989</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>0.063118499</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>-6892.56577465964</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <f aca="false">D16-C16-B16</f>
+        <v>-6892.55391716964</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <f aca="false">A16/10</f>
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <f aca="false">627.5*(B16-2*B$1)</f>
+        <v>-0.750644992500007</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <f aca="false">627.5*(C16-2*C$1)</f>
+        <v>0.00035830249999428</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <f aca="false">627.5*(D16-2*D$1)</f>
+        <v>-1.37348970799621</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <f aca="false">627.5*(E16-2*E$1)</f>
+        <v>-0.62320301745558</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B17" s="0" t="n">
         <v>-0.074199005</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C17" s="0" t="n">
         <v>0.06311793</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D17" s="0" t="n">
         <v>-6892.56413051096</v>
       </c>
-      <c r="F16" s="0" t="n">
-        <f aca="false">A16/10</f>
+      <c r="E17" s="0" t="n">
+        <f aca="false">D17-C17-B17</f>
+        <v>-6892.55304943596</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <f aca="false">A17/10</f>
         <v>18</v>
       </c>
-      <c r="G16" s="0" t="n">
-        <f aca="false">D16-C16-B16-2*(D$1-C$1-B$1)</f>
-        <v>-0.000125418529933086</v>
-      </c>
-      <c r="H16" s="0" t="n">
-        <f aca="false">C16-2*C$1</f>
-        <v>1.99999999894729E-009</v>
-      </c>
-      <c r="I16" s="0" t="n">
-        <f aca="false">B16-2*B$1</f>
-        <v>-0.000419263000000003</v>
+      <c r="H17" s="1" t="n">
+        <f aca="false">627.5*(B17-2*B$1)</f>
+        <v>-0.263087532500002</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <f aca="false">627.5*(C17-2*C$1)</f>
+        <v>1.25499999933942E-006</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <f aca="false">627.5*(D17-2*D$1)</f>
+        <v>-0.341786411554494</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <f aca="false">627.5*(E17-2*E$1)</f>
+        <v>-0.0787001338107984</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
